--- a/output/Vendor_Billing_Audit.xlsx
+++ b/output/Vendor_Billing_Audit.xlsx
@@ -9,7 +9,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Vendor" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Issue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dispute List" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stop or Recover" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Month" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dispute List" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accuracy Check" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -544,6 +547,8 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,6 +611,48 @@
       </c>
       <c r="B6" t="n">
         <v>344514.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Can still stop - pending invoices ($)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>189842.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Need to recover - approved invoices ($)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>367397.64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Audit check - planted problems caught</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>457 of 457</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Audit check - false alarms</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -629,6 +676,8 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,6 +916,8 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -949,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -959,48 +1010,334 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>invoice_id</t>
+          <t>what_to_do</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>vendor_name</t>
+          <t>flagged_invoices</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>issue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>overbilled</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>invoice_date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>amount_billed</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>approval_status</t>
+          <t>dollars</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>367</v>
+      </c>
+      <c r="C2" t="n">
+        <v>367397.64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3" t="n">
+        <v>189842.36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12395.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>flagged_invoices</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>overbilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16483.32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14264.39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13874.01</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>26133.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C6" t="n">
+        <v>27392.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18124.74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27563.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15594.22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14742.93</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C11" t="n">
+        <v>16640.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12777.41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>36</v>
+      </c>
+      <c r="C13" t="n">
+        <v>21530.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H458"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vendor_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>issue</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>overbilled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>invoice_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>amount_billed</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>what_to_do</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>INV01300</t>
         </is>
       </c>
@@ -1030,6 +1367,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1063,6 +1405,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1096,6 +1443,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1129,6 +1481,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1162,6 +1519,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1195,6 +1557,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1228,6 +1595,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1261,6 +1633,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1294,6 +1671,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1327,6 +1709,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1360,6 +1747,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1393,6 +1785,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1426,6 +1823,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1459,6 +1861,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1492,6 +1899,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1525,6 +1937,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1558,6 +1975,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1591,6 +2013,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1624,6 +2051,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1657,6 +2089,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1690,6 +2127,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1723,6 +2165,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1756,6 +2203,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1789,6 +2241,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1822,6 +2279,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1855,6 +2317,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1888,6 +2355,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1921,6 +2393,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1954,6 +2431,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1987,6 +2469,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2020,6 +2507,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2053,6 +2545,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2086,6 +2583,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2119,6 +2621,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2152,6 +2659,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2185,6 +2697,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2218,6 +2735,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2251,6 +2773,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2284,6 +2811,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2317,6 +2849,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2350,6 +2887,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2383,6 +2925,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2416,6 +2963,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2449,6 +3001,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2482,6 +3039,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2515,6 +3077,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2548,6 +3115,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2581,6 +3153,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2614,6 +3191,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2647,6 +3229,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2680,6 +3267,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2713,6 +3305,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2746,6 +3343,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2779,6 +3381,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2812,6 +3419,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2845,6 +3457,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2878,6 +3495,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2911,6 +3533,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2944,6 +3571,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2977,6 +3609,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3010,6 +3647,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3043,6 +3685,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3076,6 +3723,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3109,6 +3761,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3142,6 +3799,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3175,6 +3837,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3208,6 +3875,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3241,6 +3913,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3274,6 +3951,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3307,6 +3989,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3340,6 +4027,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3373,6 +4065,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3406,6 +4103,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3439,6 +4141,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3472,6 +4179,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3505,6 +4217,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3538,6 +4255,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3571,6 +4293,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3604,6 +4331,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3637,6 +4369,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3670,6 +4407,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3703,6 +4445,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3736,6 +4483,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3769,6 +4521,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3802,6 +4559,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3835,6 +4597,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3868,6 +4635,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3901,6 +4673,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3934,6 +4711,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3967,6 +4749,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4000,6 +4787,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4033,6 +4825,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4066,6 +4863,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4099,6 +4901,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4132,6 +4939,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4165,6 +4977,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4198,6 +5015,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4231,6 +5053,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4264,6 +5091,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4297,6 +5129,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4330,6 +5167,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4363,6 +5205,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4396,6 +5243,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4429,6 +5281,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4462,6 +5319,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4495,6 +5357,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4528,6 +5395,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4561,6 +5433,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4594,6 +5471,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4627,6 +5509,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4660,6 +5547,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4693,6 +5585,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4726,6 +5623,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4759,6 +5661,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4792,6 +5699,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4825,6 +5737,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4858,6 +5775,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4891,6 +5813,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4924,6 +5851,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4957,6 +5889,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4990,6 +5927,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5023,6 +5965,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5056,6 +6003,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5089,6 +6041,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5122,6 +6079,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5155,6 +6117,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5188,6 +6155,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5221,6 +6193,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5254,6 +6231,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5287,6 +6269,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5320,6 +6307,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5353,6 +6345,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5386,6 +6383,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5419,6 +6421,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5452,6 +6459,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5485,6 +6497,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5518,6 +6535,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5551,6 +6573,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5584,6 +6611,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5617,6 +6649,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5650,6 +6687,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5683,6 +6725,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5716,6 +6763,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5749,6 +6801,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5782,6 +6839,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5815,6 +6877,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5848,6 +6915,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5881,6 +6953,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5914,6 +6991,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5947,6 +7029,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5980,6 +7067,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6013,6 +7105,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6046,6 +7143,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6079,6 +7181,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6112,6 +7219,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6145,6 +7257,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6178,6 +7295,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6211,6 +7333,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6244,6 +7371,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6277,6 +7409,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6310,6 +7447,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6343,6 +7485,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6376,6 +7523,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6409,6 +7561,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6442,6 +7599,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6475,6 +7637,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6508,6 +7675,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6541,6 +7713,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6574,6 +7751,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6607,6 +7789,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6640,6 +7827,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6673,6 +7865,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6706,6 +7903,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6739,6 +7941,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6772,6 +7979,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6805,6 +8017,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6838,6 +8055,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6871,6 +8093,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6904,6 +8131,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6937,6 +8169,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6970,6 +8207,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7003,6 +8245,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7036,6 +8283,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7069,6 +8321,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7102,6 +8359,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7135,6 +8397,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7168,6 +8435,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7201,6 +8473,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7234,6 +8511,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7267,6 +8549,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7300,6 +8587,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7333,6 +8625,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7366,6 +8663,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7399,6 +8701,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7432,6 +8739,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7465,6 +8777,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7498,6 +8815,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7531,6 +8853,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7564,6 +8891,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7597,6 +8929,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7630,6 +8967,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7663,6 +9005,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7696,6 +9043,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7729,6 +9081,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7762,6 +9119,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7795,6 +9157,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7828,6 +9195,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7861,6 +9233,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7894,6 +9271,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7927,6 +9309,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7960,6 +9347,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7993,6 +9385,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8026,6 +9423,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8059,6 +9461,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8092,6 +9499,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8125,6 +9537,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8158,6 +9575,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8191,6 +9613,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8224,6 +9651,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8257,6 +9689,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8290,6 +9727,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8323,6 +9765,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8356,6 +9803,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8389,6 +9841,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8422,6 +9879,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8455,6 +9917,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8488,6 +9955,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8521,6 +9993,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8554,6 +10031,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8587,6 +10069,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8620,6 +10107,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8653,6 +10145,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8686,6 +10183,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8719,6 +10221,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8752,6 +10259,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8785,6 +10297,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8818,6 +10335,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8851,6 +10373,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8884,6 +10411,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8917,6 +10449,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8950,6 +10487,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8983,6 +10525,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9016,6 +10563,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9049,6 +10601,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9082,6 +10639,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9115,6 +10677,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9148,6 +10715,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9181,6 +10753,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9214,6 +10791,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9247,6 +10829,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9280,6 +10867,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9313,6 +10905,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9346,6 +10943,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9379,6 +10981,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9412,6 +11019,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9445,6 +11057,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9478,6 +11095,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9511,6 +11133,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9544,6 +11171,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9577,6 +11209,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9610,6 +11247,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9643,6 +11285,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9676,6 +11323,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9709,6 +11361,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9742,6 +11399,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9775,6 +11437,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9808,6 +11475,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9841,6 +11513,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9874,6 +11551,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9907,6 +11589,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9940,6 +11627,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9973,6 +11665,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10006,6 +11703,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10039,6 +11741,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10072,6 +11779,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10105,6 +11817,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10138,6 +11855,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10171,6 +11893,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10204,6 +11931,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10237,6 +11969,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10270,6 +12007,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10303,6 +12045,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10336,6 +12083,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10369,6 +12121,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10402,6 +12159,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10435,6 +12197,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10468,6 +12235,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10501,6 +12273,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10534,6 +12311,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10567,6 +12349,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10600,6 +12387,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10633,6 +12425,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10666,6 +12463,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10699,6 +12501,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10732,6 +12539,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10765,6 +12577,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10798,6 +12615,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10831,6 +12653,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10864,6 +12691,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10897,6 +12729,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10930,6 +12767,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10963,6 +12805,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10996,6 +12843,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11029,6 +12881,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11062,6 +12919,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11095,6 +12957,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11128,6 +12995,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11161,6 +13033,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11194,6 +13071,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11227,6 +13109,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11260,6 +13147,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11293,6 +13185,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11326,6 +13223,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11359,6 +13261,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11392,6 +13299,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11425,6 +13337,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11458,6 +13375,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11491,6 +13413,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11524,6 +13451,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11557,6 +13489,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11590,6 +13527,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11623,6 +13565,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11656,6 +13603,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11689,6 +13641,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11722,6 +13679,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11755,6 +13717,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11788,6 +13755,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11821,6 +13793,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11854,6 +13831,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11887,6 +13869,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11920,6 +13907,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11953,6 +13945,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11986,6 +13983,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12019,6 +14021,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12052,6 +14059,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12085,6 +14097,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12118,6 +14135,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12151,6 +14173,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12184,6 +14211,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12217,6 +14249,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12250,6 +14287,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12283,6 +14325,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12316,6 +14363,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12349,6 +14401,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12382,6 +14439,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12415,6 +14477,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12448,6 +14515,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12481,6 +14553,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12514,6 +14591,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12547,6 +14629,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12580,6 +14667,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12613,6 +14705,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12646,6 +14743,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12679,6 +14781,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12712,6 +14819,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12745,6 +14857,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12778,6 +14895,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12811,6 +14933,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12844,6 +14971,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12877,6 +15009,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12910,6 +15047,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12943,6 +15085,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12976,6 +15123,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13009,6 +15161,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13042,6 +15199,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13075,6 +15237,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13108,6 +15275,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13141,6 +15313,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13174,6 +15351,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13207,6 +15389,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13240,6 +15427,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13273,6 +15465,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13306,6 +15503,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13339,6 +15541,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13372,6 +15579,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13405,6 +15617,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13438,6 +15655,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13471,6 +15693,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13504,6 +15731,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13537,6 +15769,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13570,6 +15807,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13603,6 +15845,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13636,6 +15883,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13669,6 +15921,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13702,6 +15959,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13735,6 +15997,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13768,6 +16035,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13801,6 +16073,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13834,6 +16111,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13867,6 +16149,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13900,6 +16187,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13933,6 +16225,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13966,6 +16263,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13999,6 +16301,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -14032,6 +16339,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -14065,6 +16377,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -14098,6 +16415,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14131,6 +16453,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14164,6 +16491,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14197,6 +16529,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14230,6 +16567,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14263,6 +16605,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14296,6 +16643,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14329,6 +16681,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14362,6 +16719,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14395,6 +16757,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14428,6 +16795,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14461,6 +16833,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14494,6 +16871,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14527,6 +16909,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14560,6 +16947,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14593,6 +16985,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14626,6 +17023,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14659,6 +17061,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14692,6 +17099,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14725,6 +17137,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14758,6 +17175,11 @@
           <t>Rejected</t>
         </is>
       </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Already rejected</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14791,6 +17213,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14824,6 +17251,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14857,6 +17289,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14890,6 +17327,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -14923,6 +17365,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14956,6 +17403,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14989,6 +17441,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -15022,6 +17479,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15055,6 +17517,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15088,6 +17555,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15121,6 +17593,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15154,6 +17631,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15187,6 +17669,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15220,6 +17707,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -15253,6 +17745,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -15286,6 +17783,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15319,6 +17821,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15352,6 +17859,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15385,6 +17897,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15418,6 +17935,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15451,6 +17973,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15484,6 +18011,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15517,6 +18049,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15550,6 +18087,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15583,6 +18125,11 @@
           <t>Pending Review</t>
         </is>
       </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Can still stop</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15616,6 +18163,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15649,6 +18201,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15682,6 +18239,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15715,6 +18277,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15748,6 +18315,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15781,6 +18353,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15814,6 +18391,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15847,6 +18429,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15880,6 +18467,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15913,6 +18505,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15946,6 +18543,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15979,6 +18581,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16012,6 +18619,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16045,6 +18657,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16077,6 +18694,184 @@
         <is>
           <t>Approved</t>
         </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Need to recover</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>planted_problem</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>should_be_flagged_as</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>planted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>caught</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rate_small</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rate above contract</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>164</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rate_large</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rate above contract</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>padding</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quantity above usage</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>96</v>
+      </c>
+      <c r="D4" t="n">
+        <v>96</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Unexplained fee</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Likely duplicate</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>457</v>
+      </c>
+      <c r="D7" t="n">
+        <v>457</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
